--- a/fixtures/workbooks/atlantic-originations-2026Q2.xlsx
+++ b/fixtures/workbooks/atlantic-originations-2026Q2.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ironwood Fitness LLC</t>
+          <t>Foundry Upholstery LLC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -460,21 +460,21 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46191</v>
+        <v>46116</v>
       </c>
       <c r="D2" t="n">
-        <v>120000</v>
+        <v>15000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26283</t>
+          <t>81561</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kestrel Bakery LLC</t>
+          <t>Harbor Dental LLC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -483,44 +483,44 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46194</v>
+        <v>46117</v>
       </c>
       <c r="D3" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>65413</t>
+          <t>57513</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ironwood Upholstery LLC</t>
+          <t>Foundry Logistics LLC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46203</v>
+        <v>46118</v>
       </c>
       <c r="D4" t="n">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>55476</t>
+          <t>84161</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ironwood Catering LLC</t>
+          <t>Meridian Dental LLC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -529,21 +529,21 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46202</v>
+        <v>46119</v>
       </c>
       <c r="D5" t="n">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>94106</t>
+          <t>38613</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Meridian Bakery LLC</t>
+          <t>Meridian Upholstery LLC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -552,21 +552,21 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46185</v>
+        <v>46120</v>
       </c>
       <c r="D6" t="n">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>93732</t>
+          <t>57728</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Foundry Logistics LLC</t>
+          <t>Copper Bakery LLC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -575,21 +575,21 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46155</v>
+        <v>46121</v>
       </c>
       <c r="D7" t="n">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>93484</t>
+          <t>53911</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cedar Bakery LLC</t>
+          <t>Blue Ridge Catering LLC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -598,44 +598,44 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46201</v>
+        <v>46122</v>
       </c>
       <c r="D8" t="n">
-        <v>15000</v>
+        <v>75000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>92478</t>
+          <t>81794</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ironwood Logistics LLC</t>
+          <t>Kestrel Dental LLC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46178</v>
+        <v>46123</v>
       </c>
       <c r="D9" t="n">
-        <v>120000</v>
+        <v>15000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>82395</t>
+          <t>60371</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lantern Catering LLC</t>
+          <t>Meridian Print Shop LLC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -644,113 +644,113 @@
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46164</v>
+        <v>46124</v>
       </c>
       <c r="D10" t="n">
-        <v>75000</v>
+        <v>40000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72779</t>
+          <t>30261</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Harbor Print Shop LLC</t>
+          <t>Ironwood Upholstery LLC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46183</v>
+        <v>46125</v>
       </c>
       <c r="D11" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>53874</t>
+          <t>68688</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ironwood Bakery LLC</t>
+          <t>Harbor Roofing LLC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46132</v>
+        <v>46126</v>
       </c>
       <c r="D12" t="n">
-        <v>120000</v>
+        <v>15000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>57277</t>
+          <t>84137</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kestrel Catering LLC</t>
+          <t>Cedar Bakery LLC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46194</v>
+        <v>46127</v>
       </c>
       <c r="D13" t="n">
-        <v>15000</v>
+        <v>75000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>13509</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ironwood Logistics LLC</t>
+          <t>Harbor Point Marine, L.L.C.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46151</v>
+        <v>46133</v>
       </c>
       <c r="D14" t="n">
-        <v>25000</v>
+        <v>52000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>63131</t>
+          <t>48201</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cedar Dental LLC</t>
+          <t>Kestrel Holdings LLC dba Kestrel Coffee Roasters</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -759,21 +759,21 @@
         </is>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46172</v>
+        <v>46135</v>
       </c>
       <c r="D15" t="n">
-        <v>25000</v>
+        <v>31000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>48835</t>
+          <t>48202</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Harbor Point Marine, L.L.C.</t>
+          <t>Ironwood Custom Cabinetry</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -782,21 +782,21 @@
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46123</v>
+        <v>46144</v>
       </c>
       <c r="D16" t="n">
-        <v>52000</v>
+        <v>68000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>48201</t>
+          <t>48203</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kestrel Holdings LLC dba Kestrel Coffee Roasters</t>
+          <t>Meridian Freight Services</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46135</v>
+        <v>46157</v>
       </c>
       <c r="D17" t="n">
-        <v>31000</v>
+        <v>90000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>48202</t>
+          <t>48204</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ironwood Custom Cabinetry</t>
+          <t>Cedar Ridge Bakery &amp; Cafe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -828,21 +828,21 @@
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46144</v>
+        <v>46163</v>
       </c>
       <c r="D18" t="n">
-        <v>68000</v>
+        <v>33000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48203</t>
+          <t>50101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Meridian Freight Services</t>
+          <t>NW Ironwood Supply Co</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -851,21 +851,21 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="D19" t="n">
-        <v>90000</v>
+        <v>47000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>48204</t>
+          <t>50102</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Capital Investment Group</t>
+          <t>The Foundry Works</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,48 +877,64 @@
         <v>46165</v>
       </c>
       <c r="D20" t="n">
-        <v>44000</v>
+        <v>59000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>48205</t>
+          <t>50103</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Verdent Landscaping</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46118</v>
+        <v>46166</v>
       </c>
       <c r="D21" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>21000</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>50104</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Verdant Tile Works</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>Capital Investment Group</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
       <c r="C22" s="1" t="n">
-        <v>46119</v>
+        <v>46167</v>
       </c>
       <c r="D22" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
+        <v>44000</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>50105</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A100234</t>
+          <t>Blue Ridge Tannery</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -927,77 +943,130 @@
         </is>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46120</v>
+        <v>46168</v>
       </c>
       <c r="D23" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
+        <v>26000</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>50106</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Lantern Street Bakery LLC</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46173</v>
+        <v>46118</v>
       </c>
       <c r="D24" t="n">
-        <v>27000</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>48206</t>
-        </is>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lantern Street Bakery LLC</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
+          <t>Verdant Tile Works</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" s="1" t="n">
-        <v>46173</v>
+        <v>46119</v>
       </c>
       <c r="D25" t="n">
-        <v>27000</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>48206</t>
-        </is>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>A100234</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lantern Street Bakery LLC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D27" t="n">
+        <v>27000</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>48206</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Lantern Street Bakery LLC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D28" t="n">
+        <v>27000</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>48206</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Copper Ridge Fitness</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D29" t="n">
         <v>22000</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>48207</t>
         </is>

--- a/fixtures/workbooks/atlantic-originations-2026Q2.xlsx
+++ b/fixtures/workbooks/atlantic-originations-2026Q2.xlsx
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Foundry Upholstery LLC</t>
+          <t>Harbor Dental LLC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,14 +467,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>81561</t>
+          <t>57513</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Harbor Dental LLC</t>
+          <t>Foundry Logistics LLC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -486,18 +486,18 @@
         <v>46117</v>
       </c>
       <c r="D3" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57513</t>
+          <t>84161</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Foundry Logistics LLC</t>
+          <t>Meridian Dental LLC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,14 +513,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>84161</t>
+          <t>38613</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Meridian Dental LLC</t>
+          <t>Meridian Upholstery LLC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -532,18 +532,18 @@
         <v>46119</v>
       </c>
       <c r="D5" t="n">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38613</t>
+          <t>57728</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Meridian Upholstery LLC</t>
+          <t>Copper Bakery LLC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -555,18 +555,18 @@
         <v>46120</v>
       </c>
       <c r="D6" t="n">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>57728</t>
+          <t>53911</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Copper Bakery LLC</t>
+          <t>Blue Ridge Catering LLC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -578,18 +578,18 @@
         <v>46121</v>
       </c>
       <c r="D7" t="n">
-        <v>40000</v>
+        <v>75000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>53911</t>
+          <t>81794</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Blue Ridge Catering LLC</t>
+          <t>Kestrel Dental LLC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -601,18 +601,18 @@
         <v>46122</v>
       </c>
       <c r="D8" t="n">
-        <v>75000</v>
+        <v>15000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>60371</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kestrel Dental LLC</t>
+          <t>Meridian Print Shop LLC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -624,18 +624,18 @@
         <v>46123</v>
       </c>
       <c r="D9" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>60371</t>
+          <t>30261</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Meridian Print Shop LLC</t>
+          <t>Ironwood Upholstery LLC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,14 +651,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30261</t>
+          <t>68688</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ironwood Upholstery LLC</t>
+          <t>Harbor Roofing LLC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -670,18 +670,18 @@
         <v>46125</v>
       </c>
       <c r="D11" t="n">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>68688</t>
+          <t>84137</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Harbor Roofing LLC</t>
+          <t>Cedar Bakery LLC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -693,18 +693,18 @@
         <v>46126</v>
       </c>
       <c r="D12" t="n">
-        <v>15000</v>
+        <v>75000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84137</t>
+          <t>13509</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cedar Bakery LLC</t>
+          <t>Verdant Dental LLC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -716,11 +716,11 @@
         <v>46127</v>
       </c>
       <c r="D13" t="n">
-        <v>75000</v>
+        <v>15000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>58228</t>
         </is>
       </c>
     </row>
